--- a/human_resources_forms/009_customer_service_award_nomination--human_resources_forms.xlsx
+++ b/human_resources_forms/009_customer_service_award_nomination--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'a',_'name':_'customer_service',_'label':_'customer_service',_'value':_'customer_service'}</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 'A', 'name': 'Customer Service', 'label': 'Customer Service', 'value': 'Customer Service'}</t>
+          <t>Customer Service</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'b',_'name':_'other',_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 'B', 'name': 'Other', 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'c',_'name':_'team_player',_'label':_'team_player',_'value':_'team_player'}</t>
+          <t>team_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 'C', 'name': 'Team Player', 'label': 'Team Player', 'value': 'Team Player'}</t>
+          <t>Team Player</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'a',_'name':_'terms_of_service_1',_'label':_'terms_of_service_1',_'value':_'terms_of_service_1'}</t>
+          <t>terms_of_service_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'A', 'name': 'terms_of_service_1', 'label': 'terms of service 1', 'value': 'terms of service 1'}</t>
+          <t>terms of service 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'b',_'name':_'terms_of_service_2',_'label':_'terms_of_service_2',_'value':_'terms_of_service_2'}</t>
+          <t>terms_of_service_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'B', 'name': 'terms_of_service_2', 'label': 'terms of service 2', 'value': 'terms of service 2'}</t>
+          <t>terms of service 2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'c',_'name':_'terms_of_service_3',_'label':_'terms_of_service_3',_'value':_'terms_of_service_3'}</t>
+          <t>terms_of_service_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 'C', 'name': 'terms_of_service_3', 'label': 'terms of service 3', 'value': 'terms of service 3'}</t>
+          <t>terms of service 3</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'a',_'name':_'pending',_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 'A', 'name': 'pending', 'label': 'pending', 'value': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'b',_'name':_'approved',_'label':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 'B', 'name': 'approved', 'label': 'approved', 'value': 'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'c',_'name':_'rejected',_'label':_'rejected',_'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 'C', 'name': 'rejected', 'label': 'rejected', 'value': 'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
     </row>
